--- a/temp_unlock_and_upgrade.xlsx
+++ b/temp_unlock_and_upgrade.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{03E03904-1CC2-41B3-8394-669301C2CE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="7740" windowWidth="14580" windowHeight="7845" xr2:uid="{8414044E-7F7D-4D83-AA5B-315C61CD5F34}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8414044E-7F7D-4D83-AA5B-315C61CD5F34}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/temp_unlock_and_upgrade.xlsx
+++ b/temp_unlock_and_upgrade.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Unity_Project\Team_one_cubed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03E03904-1CC2-41B3-8394-669301C2CE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1ADCA9A8-DEDC-4204-9FAF-12BC5C7E858F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8414044E-7F7D-4D83-AA5B-315C61CD5F34}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8414044E-7F7D-4D83-AA5B-315C61CD5F34}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="temp_unlock_and_upgrade" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>아이스티</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,6 +62,30 @@
   </si>
   <si>
     <t>에스프레소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼음물이다.\n이가 시릴 순 있지만 더운 날에 이만한 게 없다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특유의 달콤함과 시원함으로\n시원한 기분전환을 맡는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으 쓰다!\n기운 없을 때 마시면\n거짓말처럼 힘이 솟는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뜨겁지 않아 물처럼 마실 수 있다.\n하지만 남용은 금물!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양은 얼마 안되지만\n아메리카노보다 더 쓰다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이스티와 아메리카노 두 맛을 즐길 수 있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -446,76 +470,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B3979E-47E6-42E9-9084-70F7A82AB2DC}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="1" max="1" width="3.625" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
+    <col min="5" max="5" width="50.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
-      </c>
-      <c r="B1">
-        <v>0</v>
       </c>
       <c r="C1">
         <v>0</v>
       </c>
+      <c r="D1">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>300</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>300</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>1</v>
       </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>1000</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>1</v>
       </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>2000</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
